--- a/www/download/COUNTRY.CZE.WIOD13.xlsx
+++ b/www/download/COUNTRY.CZE.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>26.5322375111802</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27.1370408253621</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>31.5159153924822</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>32.1646826403424</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>34.518468120635</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>38.431975719047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>38.008361220193</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>32.5839042490637</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28.1610815462506</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>25.6476028977032</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>23.9291690489315</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>22.5580866760044</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>20.2224473160373</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.9492103310518</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.9405056976826</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.148</t>
+          <t>1.64720228198353</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.195</t>
+          <t>0.843813326582864</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.205</t>
+          <t>0.99383873662643</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>0.983854152417042</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.949</t>
+          <t>0.977179682645578</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1.09748807792617</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>0.87672224827934</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.991</t>
+          <t>0.806492018388578</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>0.818882028086922</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.543283588585614</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.992</t>
+          <t>0.49955802960866</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.088</t>
+          <t>0.552474735579245</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5.224</t>
+          <t>0.521270117156951</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.349</t>
+          <t>0.614250668190158</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.232</t>
+          <t>0.849137001520768</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.436</t>
+          <t>3.91751869350779</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>2.44928223291742</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.419</t>
+          <t>2.71438299820255</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>2.65137146232832</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>2.65735563543749</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t>2.86161526637351</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.099</t>
+          <t>2.53233149803632</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>2.40956761606521</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>2.10391727225272</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.011</t>
+          <t>1.9260516738534</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>1.84547027913159</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>1.96822637695465</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>1.92974540910067</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>1.99168247563141</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.254</t>
+          <t>2.47285504090424</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>5.80945168629935</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>3.77055814136859</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>4.14819220859266</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>4.04202242669398</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>4.03680882957648</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>4.20876521352368</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>3.8754751920783</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>3.55875338527067</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>1.89672300483476</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>2.91649585515775</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>2.7977519437518</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>2.95802461018871</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>2.68383853573854</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>2.66614530699655</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>3.31155373902207</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>13536978815.8966</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>13873056899.9792</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>14192156486.53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>13593682845.5343</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>13128188832.8413</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>12505423876.4485</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>12818536283.7923</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>12957880163.8435</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>12895166105.5861</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>13225516486.4417</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>13216545524.8362</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>14203706156.2108</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>14758291466.8056</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>14259640022.0186</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>11833550745.0354</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>1871823172.07116</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2675441645.77356</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2469459701.27879</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2447591717.25913</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>2398355986.40787</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>2269561953.76971</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>2381088825.99375</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>2436875816.46255</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>2608992076.88731</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>2841310328.47695</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>3015906480.33118</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>2958885776.95596</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>3084818541.81761</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>3065587136.59095</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>2626578649.59065</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>3470455.04774819</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>3229520.11654104</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>3522017.243147</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>3221969.80487901</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>3280199.16645555</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.12</t>
+          <t>3224787.23627119</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>3001447.66521143</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.85</t>
+          <t>2591182.43606391</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>2103235.98831011</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>1762484.98245971</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>1621486.64863158</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>1478915.08800615</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>1235248.8078125</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>971359.84774349</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>1036572.54416026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>49846.1216488528</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>50864.3650778949</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>50237.4185401929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>49024.6496012733</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>48189.8467880837</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>49360.8750256014</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>46180.2291707587</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>46422.4499701225</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>48927.3913113244</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>54117.5722418714</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>58589.2703617767</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>62174.5060422472</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>71453.1260022088</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>80809.6620209815</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>71054.1475589423</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>105389.076500301</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>108808.533487822</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>110596.438650563</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>105351.562316628</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>103953.260943664</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>103029.290189538</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>102841.583682191</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>106278.916820354</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>113924.864804174</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>128767.466358829</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>137815.932661298</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>155227.949523824</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>182465.958222814</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>195184.811652445</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>151089.589956127</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>3.58455805443664</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>2.21223675858389</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>2.46071247713598</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>2.40608686539258</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>2.3930771937607</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>2.56668166143455</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>2.23984217463219</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>80.98</t>
+          <t>2.10629164968625</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>1.82052562182535</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>1.63321676798694</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>81.68</t>
+          <t>1.54842517502599</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>81.33</t>
+          <t>1.64707582191896</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>81.21</t>
+          <t>1.6030912000641</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>1.66067335116443</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>79.99</t>
+          <t>2.04688528031083</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19369.6008563163</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>21531.1527205147</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19707.8033997415</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>20622.5254214358</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>18632.7936569475</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>18338.4306873855</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>19010.4074538177</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>21964.3076817113</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>25203.7510737802</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>28722.905552541</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>30470.7354264256</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>32745.0861898034</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>37625.375953916</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.5322375111802</t>
+          <t>422.004465299178</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.1370408253621</t>
+          <t>601.688778720231</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.5159153924822</t>
+          <t>558.839988404089</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>32.1646826403424</t>
+          <t>569.096071503022</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>34.518468120635</t>
+          <t>584.593016541642</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>38.431975719047</t>
+          <t>555.851021241455</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38.008361220193</t>
+          <t>580.887968186227</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.5839042490637</t>
+          <t>596.49161257806</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28.1610815462506</t>
+          <t>655.333493140909</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.6476028977032</t>
+          <t>708.369118598593</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23.9291690489315</t>
+          <t>738.40892923007</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22.5580866760044</t>
+          <t>711.164628578423</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20.2224473160373</t>
+          <t>720.842943225924</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.9492103310518</t>
+          <t>707.04234674441</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.9405056976826</t>
+          <t>617.447403258456</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-594902601.482615</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-314036191.418736</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-542678690.14859</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-420897789.838622</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-387605110.793562</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-481030694.666836</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-119864031.38584</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>166546459.380001</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>488710573.788824</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1196400944.11545</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1408568451.22527</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1534750690.3968</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2010369832.9921</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2604253494.40388</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>2182745204.23566</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-699006526.757599</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-457742310.19192</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-614341365.18479</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-483469379.552314</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>-343447653.586585</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-441072137.463931</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-125786416.382577</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>298779394.541987</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>584212585.638656</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1404091001.72923</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>1567612561.52086</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1741322436.22598</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>2188604345.90373</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2789631803.01026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2440361835.86988</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>104103925.274984</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>143706118.773185</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>71662675.0361992</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>62571589.7136912</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>-44157457.2069775</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>-39958557.2029052</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>5922384.99673755</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>-132232935.161986</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-95502011.8498319</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>-207690057.613774</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>-159044110.295591</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>-206571745.829175</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>-178234512.91163</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-185378308.606379</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-257616631.63422</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1934.70397039557</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1932.76681223257</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1933.98452059255</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1938.39065429296</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1983.56923205922</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1982.54364395157</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>1881.98533806614</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>1852.87691525912</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1848.38490824424</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>1865.28944101795</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>1881.77990471389</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>1882.50669371392</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>1876.41992213971</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>1881.20873012761</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>1881.29140435433</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2017.27409561618</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2014.71657102644</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2018.61434067942</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2024.52556624705</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2057.64090234071</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2055.95872289702</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1964.94392563475</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1943.60764029914</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1945.48980531116</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1953.61502202972</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1965.07545248855</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>1960.28174217918</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>1947.82267450764</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>1955.65622553688</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1931.15104639132</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>164.64</t>
+          <t>25501.3563594792</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>27102.9554159455</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>99.38</t>
+          <t>26967.1371907302</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>30641.1681971173</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>99.71</t>
+          <t>30919.5145284852</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>109.74</t>
+          <t>33723.8702890759</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>37945.0674542685</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>43184.0017447542</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>53603.6437525298</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>73695.6695227233</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>85928.973087765</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>55.24</t>
+          <t>103876.178880117</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>133682.141617661</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>160845.920703747</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>121602.409514283</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>391.6</t>
+          <t>2983852645.42571</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>244.92</t>
+          <t>2855439750.71987</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>271.43</t>
+          <t>3118192619.28531</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>265.15</t>
+          <t>3186998515.54018</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>269.42</t>
+          <t>3322634748.8065</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>286.15</t>
+          <t>3439661072.03317</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>253.22</t>
+          <t>3591599032.94419</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>240.91</t>
+          <t>3662247255.84011</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>210.37</t>
+          <t>3854443637.41682</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>192.62</t>
+          <t>4408580201.71116</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>184.54</t>
+          <t>4739339276.21069</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>196.81</t>
+          <t>5167138155.83252</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>192.94</t>
+          <t>5766433611.12122</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>199.16</t>
+          <t>5681863666.52238</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>247.28</t>
+          <t>4532562471.8793</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>580.73</t>
+          <t>27596.0165001215</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>377.05</t>
+          <t>30603.8070708168</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>414.81</t>
+          <t>29732.2202731308</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>404.21</t>
+          <t>31512.8098103974</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>408.76</t>
+          <t>31669.8019193873</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>420.86</t>
+          <t>35362.2127479322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>387.53</t>
+          <t>39436.9402112373</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>355.81</t>
+          <t>44180.7672190162</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>189.65</t>
+          <t>54904.7753543763</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>291.66</t>
+          <t>72308.1610802052</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>279.77</t>
+          <t>81433.6111258701</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>295.79</t>
+          <t>98543.6789830382</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>268.34</t>
+          <t>123846.643864586</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>266.6</t>
+          <t>149210.147984136</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>331.15</t>
+          <t>110242.021836695</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>2712361999.2889</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>3060284098.02396</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>2953892730.81805</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>2891667208.94078</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>3047865825.79851</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>3201839081.75256</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>3704583020.96585</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>3982620515.00567</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>4532620593.76491</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>5419692757.9999</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>5591487418.07285</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>6099824571.82386</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>6797839603.04505</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>7260974646.14029</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>5614709671.30399</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>-2094.66014064229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>-3500.85165487135</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>-2765.08308240057</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>-871.641613280143</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>-750.287390902122</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>-1638.34245885631</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>-1491.87275696879</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>-996.765474261954</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>-1301.13160184649</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>1387.50844251806</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>4495.36196189493</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>5332.49989707869</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>9835.49775307494</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>11635.7727196113</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>11360.3876775878</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13540.883</t>
+          <t>271490646.136814</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13873.14</t>
+          <t>-204844347.304095</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14192.417</t>
+          <t>164299888.467256</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13593.374</t>
+          <t>295331306.599404</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13048.522</t>
+          <t>274768923.007985</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12505.747</t>
+          <t>237821990.280611</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12818.769</t>
+          <t>-112983988.021659</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12959.668</t>
+          <t>-320373259.165562</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12896.135</t>
+          <t>-678176956.348097</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13225.206</t>
+          <t>-1011112556.28873</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13216.855</t>
+          <t>-852148141.862163</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>14203.813</t>
+          <t>-932686415.99134</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>14760.565</t>
+          <t>-1031405991.92383</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>14260.811</t>
+          <t>-1579110979.61791</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11833.646</t>
+          <t>-1082147199.4247</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>27878.01033</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>32918.62252</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>29808.81218</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>31349.72661</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>29897.70559</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>27530.30469</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>30235.26834</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>36643.67487</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>43725.62879</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>54007.07428</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>59661.11896</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>69554.79096</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>84239.06212</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>103702.84821</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>89365.7284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6402.617</t>
+          <t>0.0360082122774279</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6485.192</t>
+          <t>0.00686579293120988</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6446.657</t>
+          <t>0.00688696791895828</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6325.73</t>
+          <t>0.0146247181341985</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6085.864</t>
+          <t>0.0209509267813011</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5991.293</t>
+          <t>0.0171925178078197</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5756.066</t>
+          <t>0.0198651144072149</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5659.98</t>
+          <t>0.0212391322543512</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5538.096</t>
+          <t>0.0221141824407653</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5558.336</t>
+          <t>0.0297611704773414</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5618.71</t>
+          <t>0.0363185912750695</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5689.107</t>
+          <t>0.0458865334509387</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5779.303</t>
+          <t>0.053916926456545</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5903.721</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5565.062</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>18220.6268033519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>27187.0100592577</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>25267.2653929607</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>26126.5752365978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>25163.5732089882</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>23884.7725715342</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>26170.0574150603</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>32666.5579290532</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>40090.0440019927</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>46874.1269933221</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>53686.4442984798</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61450.9121663255</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>74981.2805796816</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>95746.3264610447</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>83007.720834956</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1872.402</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2675.494</t>
+          <t>32631.1792220981</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2469.505</t>
+          <t>30678.5639491407</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2447.534</t>
+          <t>32059.7484407347</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2374.425</t>
+          <t>30953.1831688823</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2269.636</t>
+          <t>29538.7840449964</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2381.157</t>
+          <t>32567.5223859693</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2437.213</t>
+          <t>41127.6238857033</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2609.165</t>
+          <t>51135.9488229703</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2841.202</t>
+          <t>59309.022845279</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3015.943</t>
+          <t>67189.3686554274</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2958.965</t>
+          <t>76949.7458276835</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3085.173</t>
+          <t>93596.0911283756</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3065.701</t>
+          <t>119867.694073496</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2626.62</t>
+          <t>103968.870192087</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>358.31</t>
+          <t>245498.944834045</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>221.22</t>
+          <t>262404.984455268</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>246.06</t>
+          <t>246863.545920945</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>240.62</t>
+          <t>251535.982032188</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>242.73</t>
+          <t>232354.061230121</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>256.66</t>
+          <t>217074.06555197</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>223.97</t>
+          <t>227769.80376059</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>210.59</t>
+          <t>266309.526907654</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>182.03</t>
+          <t>310306.857222978</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>163.33</t>
+          <t>356175.937376202</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>154.84</t>
+          <t>389305.140198336</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>164.7</t>
+          <t>418461.297431486</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>160.28</t>
+          <t>480946.802273826</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>166.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>21775.8771342148</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>30143.056266772</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.522</t>
+          <t>30562.7547582315</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>29723.8298489291</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.259</t>
+          <t>30221.9533004683</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>31252.5152808888</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>32282.2501246377</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.592</t>
+          <t>33807.7953334713</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>35840.1826172663</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>37028.468444557</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>39734.8868380869</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>42832.1023575882</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>45701.8534384225</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>49687.8598339644</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>45845.1677299452</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>18220.6268033519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>25017.9801352588</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24997.9531794996</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>23988.5354534885</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>24331.4543688855</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>25213.3004591456</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25830.5575065606</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>26885.4825903074</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>28019.7303953848</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>29184.5585467041</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>31791.5898054579</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>34430.0084207251</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>37081.9917019284</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>40513.2280366051</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>37041.6996023775</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>28209.5789757852</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>23332.7710079019</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21407.9447208593</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>24301.1682592653</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>23500.8265811177</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>22070.4804250036</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>23535.0806640307</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>27620.4909442967</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>32065.9335270297</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>39323.118344721</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>44609.7496945726</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>51946.8245123165</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>63556.5493216244</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>77584.1123065039</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>67265.4924279131</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8581482000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8594152000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8546090000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8336710000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8137807000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8094805000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7714352000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7569647000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7358729000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7481786000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7685812000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7832395000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8030064000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8156526000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>8002883825.01644</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10385389000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10466783000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10506601000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10374742000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10183985000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10157388000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9751944000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9700054000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9578514000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9651583000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9808906000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9974580000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10175114000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10460522320.2866</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10103590571.8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6402617000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6485192000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6446657000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6325730000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6085864000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5991293000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5756066000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5659980000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5538096000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5558336000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5618710000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5689107000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5779303000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5903721098.81198</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5565061504.42354</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5148229</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5195164</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5204858</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5124530</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4949350</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4940463</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4962963</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4990747</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4923446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4940371</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4991618</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5088340</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5223840</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5348855.37841137</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5231900.73131227</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4435553</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4446554</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4418903</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4300841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4102608</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4083040</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4099050</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4085348</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3981167</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4011059</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4084331</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4160620</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4279460</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4335790</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4253931</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10385389000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10466783000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10506601000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10374742000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10183985000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10157388000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9751944000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9700054000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9578514000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9651583000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9808906000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9974580000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10175114000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10460522320.2866</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10103590571.8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8581482000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8594152000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8546090000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8336710000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8137807000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8094805000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7714352000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7569647000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7358729000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7481786000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7685812000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7832395000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>8030064000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>8156526000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8002883825.01644</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.166573778616233</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.169692810054207</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.174571254618226</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.180603645253425</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.183167233522844</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.164338498629227</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.196551407834206</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.199010445363947</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.204605442127207</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.204820376511823</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207445680303656</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.22328919934111</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.766760438555195</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.764606255087522</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.761221530850925</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.759783404645724</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.758548259103415</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.755796073865582</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.753244363573396</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.754922311106197</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.749235944721564</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.745383539411571</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.742689920171966</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.730952614362941</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0666657828285725</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0657009348582706</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0642072145308483</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0596129501008513</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0582845073737414</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0798654275051914</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0502042285923985</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0460672435298555</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0461586131512284</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0497960840766058</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0498643995243779</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0457581862959489</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.10022616651815</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.102469307678463</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.1048336444026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.107287624360311</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.11085272498633</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.111754106723243</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.118224859000065</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.120142272903144</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.123403193107016</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.123442430242449</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.130484887563702</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.14159480219758</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.805841222536161</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.804787187220306</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.806229363696137</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.808486122329607</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.809789865320462</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.813629861056625</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.813023399505688</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.816831842181587</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.81329555491645</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.81212231911831</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.806522264713003</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.799894088103586</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0939326109456895</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0927435051012311</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0889369919012627</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0842262533100811</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.079357409693207</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0746160322201317</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0687517414942476</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0630258849152691</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0633012519765343</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0644352506392414</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.062992847723295</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0585111096988344</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>131930.33656</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>145588.42367</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>138889.0318</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>148099.64303</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>141552.28303</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>139960.6931</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>154545.02045</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>185157.89271</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>226745.6239</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>275233.32295</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>310792.53065</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>368770.01749</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>456657.19042</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>564946.54779</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>458086.21635</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>49985.45611</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>55963.95023</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>52086.50867</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>56360.9167</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>54454.00975</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>51609.26447</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56102.60305</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>68748.11483</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>83201.88235</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>98632.14119</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>111799.11835</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>128896.57034</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>157152.64045</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>197451.80638</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>171234.36262</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6513636.35600347</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6732155.90104509</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6916439.49357942</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>7098294.2932243</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7283933.21595949</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7494372.74102545</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7750162.13301742</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7975477.2427386</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>8180646.87159439</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>8397388.0706155</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8599857.0472584</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8854511.26223221</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>9152706.06043163</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
